--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/25_Datenraum_QA_und_Zugriffe.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/25_Datenraum_QA_und_Zugriffe.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q_and_A" sheetId="1" r:id="R61c5aae09d6e4bab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zugriffe_IP_Ordner" sheetId="2" r:id="Re7d734144be34e81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordner_4_3" sheetId="3" r:id="R6116425c9d3a47da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q_and_A" sheetId="1" r:id="R60cdf7fb241246ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zugriffe_IP_Ordner" sheetId="2" r:id="Rccfb504688e043b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordner_4_3" sheetId="3" r:id="Rfc74a05924d14a17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -636,8 +636,8 @@
   <x:cols>
     <x:col min="1" max="1" width="33" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="31" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="44" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -684,10 +684,10 @@
         <x:v>05.09.2026</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>Scan 8 Seiten</x:v>
+        <x:v>Inhaltsabschrift; Papieroriginal nur im Aktenindex</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>Rechtsposition Rebenpfad bestritten</x:v>
+        <x:v>keine Signaturabbildungen; Rechtsposition bestritten</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -698,7 +698,7 @@
         <x:v>05.09.2026</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>zwei Tabellenblätter</x:v>
+        <x:v>drei Tabellenblätter</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
         <x:v>abweichende Registernummer beachten</x:v>

--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/25_Datenraum_QA_und_Zugriffe.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/25_Datenraum_QA_und_Zugriffe.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q_and_A" sheetId="1" r:id="R60cdf7fb241246ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zugriffe_IP_Ordner" sheetId="2" r:id="Rccfb504688e043b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordner_4_3" sheetId="3" r:id="Rfc74a05924d14a17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q_and_A" sheetId="1" r:id="R8636e91b85014378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zugriffe_IP_Ordner" sheetId="2" r:id="R2ea3d2144325496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordner_4_3" sheetId="3" r:id="Re063e8b7b7eb4a25"/>
   </x:sheets>
 </x:workbook>
 </file>
